--- a/data/trans_orig/P1422-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1422-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2012</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13715</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>689754</t>
+          <t>689851</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>700448</t>
+          <t>700433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>686562</t>
+          <t>687600</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>695992</t>
+          <t>695994</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1380758</t>
+          <t>1381472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1394539</t>
+          <t>1394501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17966</t>
+          <t>18565</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11251</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28064</t>
+          <t>28043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>999981</t>
+          <t>999382</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1012902</t>
+          <t>1012861</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1013773</t>
+          <t>1013675</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1025746</t>
+          <t>1025795</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2018857</t>
+          <t>2018878</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2035670</t>
+          <t>2036373</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22865</t>
+          <t>22470</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740403</t>
+          <t>740127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754835</t>
+          <t>754804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>766044</t>
+          <t>765810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>776067</t>
+          <t>776073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1511932</t>
+          <t>1512327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1529012</t>
+          <t>1529090</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17293</t>
+          <t>17299</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17136</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28428</t>
+          <t>29505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>930446</t>
+          <t>930440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>943703</t>
+          <t>943750</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1034765</t>
+          <t>1035018</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1047658</t>
+          <t>1047781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1971212</t>
+          <t>1970135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1989372</t>
+          <t>1988853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23305</t>
+          <t>23652</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>48721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37056</t>
+          <t>37842</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44014</t>
+          <t>44325</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76057</t>
+          <t>76054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3376870</t>
+          <t>3378058</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3403474</t>
+          <t>3403127</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3518042</t>
+          <t>3517256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3538481</t>
+          <t>3538501</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6905820</t>
+          <t>6905823</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6937863</t>
+          <t>6937552</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2016</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>12083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15548</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>662117</t>
+          <t>662717</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>672124</t>
+          <t>672067</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>665001</t>
+          <t>664608</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1332091</t>
+          <t>1332117</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1343819</t>
+          <t>1343820</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17681</t>
+          <t>18008</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20385</t>
+          <t>21228</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1014421</t>
+          <t>1013464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1021556</t>
+          <t>1021551</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1025232</t>
+          <t>1024905</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1039645</t>
+          <t>1038682</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2044959</t>
+          <t>2044116</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2059752</t>
+          <t>2059887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14439</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>746185</t>
+          <t>748285</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757809</t>
+          <t>758427</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>778640</t>
+          <t>778253</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1530124</t>
+          <t>1530846</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1542352</t>
+          <t>1542577</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>14052</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18136</t>
+          <t>18545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26133</t>
+          <t>26574</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>922992</t>
+          <t>923515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>934732</t>
+          <t>933898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1025643</t>
+          <t>1025234</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1040287</t>
+          <t>1039966</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1955213</t>
+          <t>1954772</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1972437</t>
+          <t>1972154</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13945</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32003</t>
+          <t>32006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34642</t>
+          <t>31761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30805</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56990</t>
+          <t>58608</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3362347</t>
+          <t>3362344</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3380746</t>
+          <t>3380405</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3509900</t>
+          <t>3512781</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3532154</t>
+          <t>3531773</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6881902</t>
+          <t>6880284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6908087</t>
+          <t>6907771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2023</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18131</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>12419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13064</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27532</t>
+          <t>27340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>617310</t>
+          <t>617905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>629018</t>
+          <t>628794</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>661976</t>
+          <t>662951</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>670467</t>
+          <t>670465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1283279</t>
+          <t>1283471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1297747</t>
+          <t>1297201</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22672</t>
+          <t>24801</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16522</t>
+          <t>16683</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>14787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34891</t>
+          <t>34219</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1170192</t>
+          <t>1168063</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1186453</t>
+          <t>1185931</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>940915</t>
+          <t>940754</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>950618</t>
+          <t>950873</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2115410</t>
+          <t>2116082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2134464</t>
+          <t>2135514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14939</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22331</t>
+          <t>22559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>686277</t>
+          <t>686570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>696882</t>
+          <t>697381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>920294</t>
+          <t>921245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>930308</t>
+          <t>930235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1611300</t>
+          <t>1611072</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1625828</t>
+          <t>1625730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17320</t>
+          <t>16406</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26867</t>
+          <t>26277</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>912646</t>
+          <t>912870</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922360</t>
+          <t>922694</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1074594</t>
+          <t>1075508</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1085128</t>
+          <t>1085270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1991878</t>
+          <t>1992468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2005945</t>
+          <t>2005988</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>30356</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55342</t>
+          <t>54428</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>25426</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45340</t>
+          <t>44643</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60051</t>
+          <t>60011</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91572</t>
+          <t>93365</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3401010</t>
+          <t>3401924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3425954</t>
+          <t>3425996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3611797</t>
+          <t>3612494</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3631145</t>
+          <t>3631711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7021918</t>
+          <t>7020125</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7053439</t>
+          <t>7053479</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/P1422-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1422-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>19731</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>689851</t>
+          <t>688995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>700433</t>
+          <t>700419</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>687600</t>
+          <t>686637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>695994</t>
+          <t>695992</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1381472</t>
+          <t>1380788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1394501</t>
+          <t>1394407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>18828</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28043</t>
+          <t>27616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>999382</t>
+          <t>999119</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1012861</t>
+          <t>1012858</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1013675</t>
+          <t>1013760</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1025795</t>
+          <t>1025752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2018878</t>
+          <t>2019305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2036373</t>
+          <t>2036404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11364</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22470</t>
+          <t>23075</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740127</t>
+          <t>739428</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754804</t>
+          <t>754718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>765810</t>
+          <t>765599</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>776073</t>
+          <t>776065</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1512327</t>
+          <t>1511722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1529090</t>
+          <t>1528740</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>19118</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17286</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29505</t>
+          <t>28972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>930440</t>
+          <t>928621</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>943750</t>
+          <t>943670</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1035018</t>
+          <t>1034615</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1047781</t>
+          <t>1047750</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1970135</t>
+          <t>1970668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1988853</t>
+          <t>1988547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23652</t>
+          <t>22359</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48721</t>
+          <t>48363</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>16530</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37842</t>
+          <t>37599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44325</t>
+          <t>44556</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76054</t>
+          <t>75941</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3378058</t>
+          <t>3378416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3403127</t>
+          <t>3404420</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3517256</t>
+          <t>3517499</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3538501</t>
+          <t>3538568</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6905823</t>
+          <t>6905936</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6937552</t>
+          <t>6937321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>662717</t>
+          <t>662869</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>672067</t>
+          <t>672074</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>664608</t>
+          <t>665893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1332117</t>
+          <t>1331537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1343820</t>
+          <t>1343727</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>879</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18008</t>
+          <t>17574</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21228</t>
+          <t>19982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1013464</t>
+          <t>1014157</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1021551</t>
+          <t>1021552</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1024905</t>
+          <t>1025339</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1038682</t>
+          <t>1039581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2044116</t>
+          <t>2045362</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2059887</t>
+          <t>2059890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11267</t>
+          <t>12704</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>748285</t>
+          <t>746848</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>758427</t>
+          <t>758459</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>778253</t>
+          <t>777845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1530846</t>
+          <t>1529049</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1542577</t>
+          <t>1542402</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14052</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>17319</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26574</t>
+          <t>25677</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>923515</t>
+          <t>923826</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>933898</t>
+          <t>933940</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1025234</t>
+          <t>1026460</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1039966</t>
+          <t>1040251</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1954772</t>
+          <t>1955669</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1972154</t>
+          <t>1972025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13945</t>
+          <t>13997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32006</t>
+          <t>32775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31761</t>
+          <t>33118</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31121</t>
+          <t>29670</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58608</t>
+          <t>58871</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3362344</t>
+          <t>3361575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3380405</t>
+          <t>3380353</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3512781</t>
+          <t>3511424</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3531773</t>
+          <t>3532233</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6880284</t>
+          <t>6880021</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6907771</t>
+          <t>6909222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19071</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27340</t>
+          <t>28973</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>624223</t>
+          <t>678608</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>617905</t>
+          <t>670266</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>628794</t>
+          <t>683366</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>667517</t>
+          <t>724583</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>662951</t>
+          <t>719327</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>670465</t>
+          <t>727922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1291740</t>
+          <t>1403190</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1283471</t>
+          <t>1394458</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1297201</t>
+          <t>1409336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24801</t>
+          <t>22278</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,17 +4999,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16683</t>
+          <t>18806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>24311</t>
+          <t>26271</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14787</t>
+          <t>18866</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34219</t>
+          <t>36513</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1179082</t>
+          <t>1034427</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1168063</t>
+          <t>1026639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1185931</t>
+          <t>1040359</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5112,17 +5112,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>946908</t>
+          <t>1058406</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>940754</t>
+          <t>1051381</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>950873</t>
+          <t>1062499</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2125990</t>
+          <t>2092833</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2116082</t>
+          <t>2082591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2135514</t>
+          <t>2100238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150301</t>
+          <t>2119104</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150301</t>
+          <t>2119104</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150301</t>
+          <t>2119104</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>17730</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5342,32 +5342,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>15730</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22559</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>692944</t>
+          <t>789472</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>686570</t>
+          <t>781639</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>697381</t>
+          <t>794117</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>926940</t>
+          <t>804364</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>921245</t>
+          <t>798757</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>930235</t>
+          <t>807692</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1619883</t>
+          <t>1593837</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1611072</t>
+          <t>1586217</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1625730</t>
+          <t>1600293</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>701216</t>
+          <t>799369</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>701216</t>
+          <t>799369</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>701216</t>
+          <t>799369</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932416</t>
+          <t>810198</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932416</t>
+          <t>810198</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932416</t>
+          <t>810198</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1633631</t>
+          <t>1609567</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1633631</t>
+          <t>1609567</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1633631</t>
+          <t>1609567</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16406</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>14974</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26277</t>
+          <t>29970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>918498</t>
+          <t>981713</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>912870</t>
+          <t>975785</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922694</t>
+          <t>985503</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1080974</t>
+          <t>1104726</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1075508</t>
+          <t>1097957</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1085270</t>
+          <t>1109649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1999473</t>
+          <t>2086439</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1992468</t>
+          <t>2077726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2005988</t>
+          <t>2092722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018745</t>
+          <t>2107696</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018745</t>
+          <t>2107696</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018745</t>
+          <t>2107696</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30356</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54428</t>
+          <t>57277</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25426</t>
+          <t>30323</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44643</t>
+          <t>50455</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>76403</t>
+          <t>83499</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60011</t>
+          <t>68425</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93365</t>
+          <t>98810</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3414746</t>
+          <t>3484220</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3401924</t>
+          <t>3471781</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3425996</t>
+          <t>3495090</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3622340</t>
+          <t>3692080</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3612494</t>
+          <t>3680286</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3631711</t>
+          <t>3700418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7037087</t>
+          <t>7176300</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7020125</t>
+          <t>7160989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7053479</t>
+          <t>7191374</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3456352</t>
+          <t>3529058</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3456352</t>
+          <t>3529058</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3456352</t>
+          <t>3529058</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657137</t>
+          <t>3730741</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657137</t>
+          <t>3730741</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657137</t>
+          <t>3730741</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7113490</t>
+          <t>7259799</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7113490</t>
+          <t>7259799</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7113490</t>
+          <t>7259799</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
